--- a/modules/confidence/docs/templates/Confidence_Config_Template.xlsx
+++ b/modules/confidence/docs/templates/Confidence_Config_Template.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
   <si>
     <t xml:space="preserve">TURAS Confidence Module - File Paths</t>
   </si>
@@ -122,9 +122,6 @@
     <t xml:space="preserve">Bootstrap_Iterations</t>
   </si>
   <si>
-    <t xml:space="preserve">5000</t>
-  </si>
-  <si>
     <t xml:space="preserve">Number of bootstrap resamples. Higher values give more precise intervals but take longer.</t>
   </si>
   <si>
@@ -179,9 +176,6 @@
     <t xml:space="preserve">Max_Questions</t>
   </si>
   <si>
-    <t xml:space="preserve">200</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maximum number of questions to process. Safety limit to prevent runaway processing.</t>
   </si>
   <si>
@@ -194,6 +188,12 @@
     <t xml:space="preserve">Generate an interactive HTML report in addition to the Excel output.</t>
   </si>
   <si>
+    <t xml:space="preserve">Generate_Stats_Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate a diagnostic stats pack workbook alongside main output. The stats pack provides a full audit trail of data received, methods used, assumptions, and reproducibility — designed for advanced partners and research statisticians. Output file is named {output}_stats_pack.xlsx.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sampling_Method</t>
   </si>
   <si>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">The sampling methodology used. Affects design effect estimation and interpretation notes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Random, Stratified, Cluster, Census, Quota, Online_Panel, Self_Selected, Not_Specified</t>
+    <t xml:space="preserve">Sampling approach used for data collection</t>
   </si>
   <si>
     <t xml:space="preserve">BRANDING</t>
@@ -245,6 +245,30 @@
     <t xml:space="preserve">Any positive integer</t>
   </si>
   <si>
+    <t xml:space="preserve">STUDY IDENTIFICATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project name — appears in the stats pack Declaration sheet for identification and sign-off purposes. Leave blank if not using stats pack.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyst_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyst name — appears in the stats pack Declaration sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research_House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research organisation name — appears in the stats pack Declaration sheet. Use your company or white-label partner name.</t>
+  </si>
+  <si>
     <t xml:space="preserve">TURAS Confidence Module - Question Analysis</t>
   </si>
   <si>
@@ -254,9 +278,6 @@
     <t xml:space="preserve">Question_ID</t>
   </si>
   <si>
-    <t xml:space="preserve">Question_Label</t>
-  </si>
-  <si>
     <t xml:space="preserve">Statistic_Type</t>
   </si>
   <si>
@@ -290,21 +311,9 @@
     <t xml:space="preserve">Prior_N</t>
   </si>
   <si>
-    <t xml:space="preserve">Filter_Variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filter_Values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
     <t xml:space="preserve">[REQUIRED] Column name in data that contains responses for this question.</t>
   </si>
   <si>
-    <t xml:space="preserve">[Optional] Human-readable label for this question. Shown alongside Question_ID in output reports.</t>
-  </si>
-  <si>
     <t xml:space="preserve">[REQUIRED] Type of statistic to compute: proportion (binary/categorical), mean (continuous), or nps (Net Promoter Score).</t>
   </si>
   <si>
@@ -338,40 +347,22 @@
     <t xml:space="preserve">[Optional] Prior effective sample size for Bayesian credible intervals. Controls how much weight is given to the prior.</t>
   </si>
   <si>
-    <t xml:space="preserve">[Optional] Column name to filter on for sub-sample analysis. E.g. 'Q04' to only include certain respondent groups.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Comma-separated values to keep from Filter_Variable. E.g. 'Daily,Weekly' to analyse only frequent users.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Free-text notes for documentation. Not used in analysis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q_SAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overall Satisfaction</t>
+    <t xml:space="preserve">Q1_Awareness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proportion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2_Satisfaction</t>
   </si>
   <si>
     <t xml:space="preserve">mean</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-10 scale. Prior from previous wave.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q_NPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Likelihood to Recommend (NPS)</t>
+    <t xml:space="preserve">Q3_NPS</t>
   </si>
   <si>
     <t xml:space="preserve">nps</t>
@@ -383,39 +374,6 @@
     <t xml:space="preserve">0,1,2,3,4,5,6</t>
   </si>
   <si>
-    <t xml:space="preserve">Standard 0-10 NPS scale.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q_AGREE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agreement with Statement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proportion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top-2-box on 5-point Likert (4=Agree, 5=Strongly Agree).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q_SUBSET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subset: Daily Users Only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q_FREQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only asked to daily users (Q_FREQ=Daily). Subset filtering applied.</t>
-  </si>
-  <si>
     <t xml:space="preserve">TURAS Confidence Module - Population Margins</t>
   </si>
   <si>
@@ -461,16 +419,13 @@
     <t xml:space="preserve">Female</t>
   </si>
   <si>
-    <t xml:space="preserve">Age_Group</t>
+    <t xml:space="preserve">AgeGroup</t>
   </si>
   <si>
     <t xml:space="preserve">18-34</t>
   </si>
   <si>
     <t xml:space="preserve">35-54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55+</t>
   </si>
 </sst>
 </file>
@@ -488,28 +443,24 @@
     </font>
     <font>
       <sz val="14"/>
-      <color rgb="FF1E3A5F"/>
+      <color rgb="FF323367"/>
       <name val="Calibri"/>
       <b/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1E3A5F"/>
+      <sz val="10"/>
+      <color rgb="FF546E7A"/>
       <name val="Calibri"/>
+      <i/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF333333"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <b/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
@@ -521,39 +472,44 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1E3A5F"/>
+      <color rgb="FF323367"/>
       <name val="Calibri"/>
       <b/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF2471A3"/>
+      <sz val="9"/>
+      <color rgb="FFD32F2F"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF546E7A"/>
       <name val="Calibri"/>
       <i/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF555555"/>
+      <sz val="10"/>
+      <color rgb="FF546E7A"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF6C757D"/>
+      <color rgb="FF388E3C"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF6C757D"/>
+      <sz val="10"/>
+      <color rgb="FF37474F"/>
       <name val="Calibri"/>
-      <i/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -562,47 +518,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDEBD0"/>
+        <fgColor rgb="FFFFF3E0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F8E8"/>
+        <fgColor rgb="FFF1F8E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF9E6"/>
+        <fgColor rgb="FFFFFDE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8E8E8"/>
+        <fgColor rgb="FFECEFF1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E3A5F"/>
+        <fgColor rgb="FF323367"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD5E3F0"/>
+        <fgColor rgb="FFE8EAF6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFF8F9FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEBF5FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9ECEF"/>
+        <fgColor rgb="FFE3F2FD"/>
       </patternFill>
     </fill>
   </fills>
@@ -616,30 +567,30 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFC0C0C0"/>
+        <color rgb="FFB0BEC5"/>
       </left>
       <right style="thin">
-        <color rgb="FFC0C0C0"/>
+        <color rgb="FFB0BEC5"/>
       </right>
       <top style="thin">
-        <color rgb="FFC0C0C0"/>
+        <color rgb="FFB0BEC5"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFC0C0C0"/>
+        <color rgb="FFB0BEC5"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FF323367"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FF323367"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FF323367"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FF323367"/>
       </bottom>
     </border>
   </borders>
@@ -648,48 +599,54 @@
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -981,10 +938,10 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="22.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="55.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="38.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="28.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="65.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="55.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="35.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1041,7 +998,7 @@
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7">
       <c r="A7" s="10" t="s">
         <v>13</v>
       </c>
@@ -1054,11 +1011,11 @@
       <c r="D7" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="14" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8">
       <c r="A8" s="10" t="s">
         <v>18</v>
       </c>
@@ -1071,45 +1028,50 @@
       <c r="D8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="14" t="s">
+    <row r="9">
+      <c r="A9" s="15" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="14" t="s">
+    <row r="10">
+      <c r="A10" s="15" t="s">
         <v>24</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="14" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A6:E6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -1120,11 +1082,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="32.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="38.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="28.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="65.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="40.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="55.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="35.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1180,7 +1142,7 @@
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7">
       <c r="A7" s="10" t="s">
         <v>30</v>
       </c>
@@ -1193,225 +1155,311 @@
       <c r="D7" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="14" t="s">
+    <row r="8">
+      <c r="A8" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="E8" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="11" t="s">
+      <c r="D9" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="E9" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D10" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="13" t="s">
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="s">
         <v>44</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="14" t="s">
-        <v>45</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D11" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="14" t="s">
         <v>46</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="14" t="s">
+    <row r="13">
+      <c r="A13" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="C13" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="E13" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="14" t="s">
+      <c r="D14" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="E14" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="15" t="s">
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="13" t="s">
+      <c r="D15" s="13" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="14" t="s">
+      <c r="E15" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="15" t="s">
+      <c r="B16" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D16" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="14" t="s">
+      <c r="E16" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B17" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C17" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D17" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E17" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="9" t="s">
+    <row r="18">
+      <c r="A18" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="14" t="s">
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B19" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C19" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D19" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E19" s="14" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="14" t="s">
+    <row r="20">
+      <c r="A20" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B20" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C20" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D20" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E20" s="14" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="s">
+    <row r="21">
+      <c r="A21" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="14" t="s">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B22" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C22" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D22" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E22" s="14" t="s">
         <v>75</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A23:E23"/>
+  </mergeCells>
   <dataValidations count="2">
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8:B8">
       <formula1>1000</formula1>
@@ -1426,8 +1474,8 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
+        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"0.90,0.95,0.99"</xm:f>
           </x14:formula1>
@@ -1437,7 +1485,13 @@
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>B9:B15</xm:sqref>
+          <xm:sqref>B9:B9</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Y,N"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B10:B10</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -1453,9 +1507,21 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
+            <xm:f>"Y,N"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B15:B15</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Y,N"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B16:B16</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
             <xm:f>"Random,Stratified,Cluster,Quota,Online_Panel,Self_Selected,Census,Not_Specified"</xm:f>
           </x14:formula1>
-          <xm:sqref>B16:B16</xm:sqref>
+          <xm:sqref>B17:B17</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1468,131 +1534,103 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="14.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="32.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="22.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="18.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="14.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="14.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="14.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="18.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="25.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="20.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="20.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="14.71" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="12.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="10.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="10.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="16.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="16.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="42.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="12.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" ht="55" customHeight="1">
-      <c r="A4" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D4" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="E4" s="16" t="s">
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="B4" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="C4" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="D4" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="E4" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="F4" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="G4" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="L4" s="16" t="s">
+      <c r="H4" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="M4" s="16" t="s">
+      <c r="I4" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="N4" s="16" t="s">
+      <c r="J4" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="O4" s="16" t="s">
+      <c r="K4" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="P4" s="16" t="s">
+      <c r="L4" s="13" t="s">
         <v>109</v>
       </c>
     </row>
@@ -1604,19 +1642,19 @@
         <v>111</v>
       </c>
       <c r="C5" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="17" t="s">
         <v>112</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>39</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>14</v>
@@ -1628,101 +1666,77 @@
         <v>14</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>113</v>
+        <v>14</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="M5" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="N5" s="17" t="s">
         <v>14</v>
-      </c>
-      <c r="O5" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="P5" s="17" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>119</v>
+        <v>38</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>14</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="K6" s="17" t="s">
         <v>14</v>
+      </c>
+      <c r="J6" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K6" s="17" t="n">
+        <v>2</v>
       </c>
       <c r="L6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="M6" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="N6" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="O6" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="P6" s="17" t="s">
-        <v>122</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>125</v>
+        <v>38</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="J7" s="17" t="s">
         <v>14</v>
@@ -1733,104 +1747,746 @@
       <c r="L7" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="O7" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="P7" s="17" t="s">
-        <v>127</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="O8" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="P8" s="17" t="s">
-        <v>132</v>
-      </c>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="11"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="11"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="11"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="11"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="11"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="11"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="11"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="11"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="11"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="11"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="11"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="11"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="11"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="11"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="11"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="11"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="11"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="11"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="11"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"proportion,mean,nps"</xm:f>
           </x14:formula1>
-          <xm:sqref>C5:C54</xm:sqref>
+          <xm:sqref>B5:B57</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Y,N"</xm:f>
+          </x14:formula1>
+          <xm:sqref>C5:C57</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>D5:D54</xm:sqref>
+          <xm:sqref>D5:D57</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>E5:E54</xm:sqref>
+          <xm:sqref>E5:E57</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>F5:F54</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"Y,N"</xm:f>
-          </x14:formula1>
-          <xm:sqref>G5:G54</xm:sqref>
+          <xm:sqref>F5:F57</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1843,145 +2499,342 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="18.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="10.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="22.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="25.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="18.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>144</v>
+      <c r="A4" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>14</v>
+        <v>132</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>0.48</v>
+        <v>0.485</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>14</v>
+        <v>133</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>2</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.52</v>
+        <v>0.515</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>14</v>
+        <v>135</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="D7" s="17" t="n">
         <v>0.3</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>14</v>
+        <v>136</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>2</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>39</v>
-      </c>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D34">
+    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="D5:D38">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -1995,7 +2848,7 @@
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>E5:E34</xm:sqref>
+          <xm:sqref>E5:E38</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
